--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sev IPM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BajoRend" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin Conv" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda NC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda No Convertida" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Corp" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Destino" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por País" sheetId="8" state="visible" r:id="rId8"/>
@@ -524,27 +524,27 @@
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Severity %NoDispo</t>
+          <t>Canasta OP · Severity %NoDispo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · P80 · target &lt;3%</t>
+          <t>B2B Opaco · P80 · target &lt;3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>39</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.002361489554950046</v>
+        <v>0.002217925386715196</v>
       </c>
     </row>
     <row r="7">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.02125340599455041</v>
+        <v>0.02007506824385805</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1630</v>
+        <v>1635</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.098698153194066</v>
+        <v>0.09298225659690627</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1193</v>
+        <v>1214</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.0722373599757796</v>
+        <v>0.06904003639672429</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13302</v>
+        <v>14343</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.805449591280654</v>
+        <v>0.8156847133757962</v>
       </c>
     </row>
   </sheetData>
@@ -683,21 +683,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Severity IPM (USD/M)</t>
+          <t>Canasta OP · Severity IPM (USD/M)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · P80 · target ≥ $650</t>
+          <t>B2B Opaco · P80 · target ≥ $650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11680</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.7072358462004239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1046</v>
+        <v>13736</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.0633363608840448</v>
+        <v>0.781164695177434</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>985</v>
+        <v>1002</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.05964274901604602</v>
+        <v>0.05698362147406733</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1249</v>
+        <v>1287</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07562821677263094</v>
+        <v>0.07319153776160145</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.09415682712685437</v>
+        <v>0.08866014558689718</v>
       </c>
     </row>
   </sheetData>
@@ -844,21 +844,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Top 50 Bajo Rendimiento</t>
+          <t>Canasta OP · Top 50 Bajo Rendimiento</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · BKGS&gt;0 · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · BKGS&gt;0 · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3452,21 +3452,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Top 50 Sin Conversión</t>
+          <t>Canasta OP · Top 50 Sin Conversión</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
+          <t>B2B Opaco · BKGS=0 · ordenado por tráfico ↓ · cohorte estructural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5497,21 +5497,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Top 50 Demanda No Convertida</t>
+          <t>Canasta OP · Top 50 Demanda No Convertida</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
+          <t>B2B Opaco · tráfico × %NoDispo · ordenado por demanda perdida ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -7850,21 +7850,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Por Corporativo</t>
+          <t>Canasta OP · Por Corporativo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · Top 50 corp · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · Top 50 corp · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
         <v>6650.84</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0.01545218050279508</v>
+        <v>0.01545218050279509</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>377.3979118628988</v>
@@ -8984,7 +8984,7 @@
         <v>1208.42</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>0.1170824743635684</v>
+        <v>0.1170824743635683</v>
       </c>
       <c r="G36" s="15" t="n">
         <v>88.56938116870511</v>
@@ -9579,7 +9579,7 @@
         <v>2530.29</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0.004535477776961692</v>
+        <v>0.004535477776961693</v>
       </c>
       <c r="G53" s="15" t="n">
         <v>432.1950086343691</v>
@@ -9693,21 +9693,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Por Destino</t>
+          <t>Canasta OP · Por Destino</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · Top 50 destinos · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · Top 50 destinos · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11530,27 +11530,27 @@
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Canasta B2B Opaco · Por País</t>
+          <t>Canasta OP · Por País</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B (OP) · todos los países · ordenado por tráfico ↓</t>
+          <t>B2B Opaco · todos los países · ordenado por tráfico ↓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 01:37 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14747,7 +14747,7 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14992,7 +14992,7 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="14" t="n">
-        <v>0.02242348302729265</v>
+        <v>0.02242348302729266</v>
       </c>
       <c r="G104" s="15" t="n">
         <v>0</v>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15202,7 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15925,7 +15925,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="14" t="n">
-        <v>0.0839205103859544</v>
+        <v>0.08392051038595441</v>
       </c>
       <c r="G129" s="15" t="n">
         <v>0</v>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16497,7 +16497,7 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16672,7 +16672,7 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16707,7 +16707,7 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16847,7 +16847,7 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17092,7 +17092,7 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17127,7 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,42 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-18/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-18/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
@@ -858,7 +858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         <v>0.03810156285010617</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>-760.4739053009391</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>0.04493012423010238</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-217.7982497779363</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>0.000774277901696027</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>-74.08525527279994</v>
+        <v>0</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>0.0288363765312982</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>-744.3343870129813</v>
+        <v>0</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>0.007429924365760854</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>-62.07961596784848</v>
+        <v>0</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>0.002569320414516403</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>-144.0592829392164</v>
+        <v>0</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>0.009001570332194167</v>
       </c>
       <c r="J34" s="15" t="n">
-        <v>-96.03823635026799</v>
+        <v>0</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>0.01376338186096557</v>
       </c>
       <c r="J38" s="15" t="n">
-        <v>-238.8407938821226</v>
+        <v>0</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>0.09161952404020585</v>
       </c>
       <c r="J40" s="15" t="n">
-        <v>-1445.54139869183</v>
+        <v>0</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>0.00420231163084198</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>-747.6110219154961</v>
+        <v>0</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>0.007306387101313574</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>-282.73788583212</v>
+        <v>0</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>0.00530354746699539</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>-449.6637739714179</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>0.05014504591837735</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>-431.3950861583672</v>
+        <v>0</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -5511,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="15" t="n">
-        <v>-859.5199346387466</v>
+        <v>0</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-762.1488953438106</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>5</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>-2305.296374975763</v>
+        <v>0</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>16</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>-6372.064675536319</v>
+        <v>0</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>5</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>-3245.428400464913</v>
+        <v>0</v>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>2</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>-1425.454278746539</v>
+        <v>0</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="15" t="n">
-        <v>-1445.54139869183</v>
+        <v>0</v>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>-503.020870219243</v>
+        <v>0</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -7864,7 +7864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
         <v>0.160994037932987</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>-346.0339140392449</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>0.006590028254454681</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>-212.4751646870261</v>
+        <v>0</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>0.02586231017404018</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>-838.472418187805</v>
+        <v>0</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>0.007898327532920395</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>-835.351585064459</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -11550,7 +11550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 19:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 19:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12323,7 +12323,7 @@
         <v>0.05909604243638321</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>-112.9392255476317</v>
+        <v>0</v>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         <v>0.04619098092631751</v>
       </c>
       <c r="G36" s="15" t="n">
-        <v>-292.867202307351</v>
+        <v>0</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>0.3144020289619772</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>-149.3786458437206</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>0.1280315232155698</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>-87.52710690951095</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>0.02328213335434506</v>
       </c>
       <c r="G50" s="15" t="n">
-        <v>-164.6868441191261</v>
+        <v>0</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>0.1104616363622615</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>-6061.394849947678</v>
+        <v>0</v>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>0.06511139609118707</v>
       </c>
       <c r="G58" s="15" t="n">
-        <v>-356.5936036713294</v>
+        <v>0</v>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>0.01500835107253971</v>
       </c>
       <c r="G70" s="15" t="n">
-        <v>-3453.59751105289</v>
+        <v>0</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>0.05148135708001245</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>-9513.865752482074</v>
+        <v>0</v>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>0.1216154367725167</v>
       </c>
       <c r="G75" s="15" t="n">
-        <v>-1826.449316306927</v>
+        <v>0</v>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>0.001823187974400953</v>
       </c>
       <c r="G106" s="15" t="n">
-        <v>-12451.13360123034</v>
+        <v>0</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
